--- a/CAP766(PYTHON).xlsx
+++ b/CAP766(PYTHON).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\asus\Desktop\776\CAP776-GROUP-I-\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68A26688-A0B3-4C5C-A6D5-FC6ACC4E35DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66FFF41E-B02C-4CEA-932B-024AEF7A043A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="81">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -266,6 +266,9 @@
   </si>
   <si>
     <t>…..........</t>
+  </si>
+  <si>
+    <t>Prep for CA TEST.</t>
   </si>
 </sst>
 </file>
@@ -2197,26 +2200,50 @@
       </c>
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A31" s="13"/>
-      <c r="B31" s="14"/>
-      <c r="C31" s="14"/>
-      <c r="D31" s="14"/>
-      <c r="E31" s="14"/>
-      <c r="F31" s="14"/>
-      <c r="G31" s="14"/>
-      <c r="H31" s="14"/>
-      <c r="I31" s="15" t="str">
+      <c r="A31" s="13">
+        <v>46271</v>
+      </c>
+      <c r="B31" s="14">
+        <v>360</v>
+      </c>
+      <c r="C31" s="14">
+        <v>0</v>
+      </c>
+      <c r="D31" s="14">
+        <v>120</v>
+      </c>
+      <c r="E31" s="14">
+        <v>0</v>
+      </c>
+      <c r="F31" s="14">
+        <v>0</v>
+      </c>
+      <c r="G31" s="14">
+        <v>0</v>
+      </c>
+      <c r="H31" s="14">
+        <v>180</v>
+      </c>
+      <c r="I31" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J31" s="15" t="str">
+        <v>660</v>
+      </c>
+      <c r="J31" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K31" s="16"/>
-      <c r="L31" s="16"/>
-      <c r="M31" s="16"/>
-      <c r="N31" s="17"/>
+        <v>780</v>
+      </c>
+      <c r="K31" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L31" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="M31" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N31" s="17" t="s">
+        <v>80</v>
+      </c>
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A32" s="13"/>

--- a/CAP766(PYTHON).xlsx
+++ b/CAP766(PYTHON).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\asus\Desktop\776\CAP776-GROUP-I-\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66FFF41E-B02C-4CEA-932B-024AEF7A043A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{714B8119-0BD3-415D-A4B0-C9846C65E92E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="82">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -269,6 +269,9 @@
   </si>
   <si>
     <t>Prep for CA TEST.</t>
+  </si>
+  <si>
+    <t>completed my First CA test in networking.</t>
   </si>
 </sst>
 </file>
@@ -2245,27 +2248,51 @@
         <v>80</v>
       </c>
     </row>
-    <row r="32" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A32" s="13"/>
-      <c r="B32" s="14"/>
-      <c r="C32" s="14"/>
-      <c r="D32" s="14"/>
-      <c r="E32" s="14"/>
-      <c r="F32" s="14"/>
-      <c r="G32" s="14"/>
-      <c r="H32" s="14"/>
-      <c r="I32" s="15" t="str">
+    <row r="32" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A32" s="13">
+        <v>46272</v>
+      </c>
+      <c r="B32" s="14">
+        <v>360</v>
+      </c>
+      <c r="C32" s="14">
+        <v>40</v>
+      </c>
+      <c r="D32" s="14">
+        <v>120</v>
+      </c>
+      <c r="E32" s="14">
+        <v>0</v>
+      </c>
+      <c r="F32" s="14">
+        <v>150</v>
+      </c>
+      <c r="G32" s="14">
+        <v>3</v>
+      </c>
+      <c r="H32" s="14">
+        <v>180</v>
+      </c>
+      <c r="I32" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J32" s="15" t="str">
+        <v>850</v>
+      </c>
+      <c r="J32" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K32" s="16"/>
-      <c r="L32" s="16"/>
-      <c r="M32" s="16"/>
-      <c r="N32" s="17"/>
+        <v>590</v>
+      </c>
+      <c r="K32" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="L32" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="M32" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N32" s="17" t="s">
+        <v>81</v>
+      </c>
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A33" s="13"/>

--- a/CAP766(PYTHON).xlsx
+++ b/CAP766(PYTHON).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\asus\Desktop\776\CAP776-GROUP-I-\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{714B8119-0BD3-415D-A4B0-C9846C65E92E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{279AE183-E3CF-492B-909D-71457E01F329}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="82">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -2294,27 +2294,51 @@
         <v>81</v>
       </c>
     </row>
-    <row r="33" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A33" s="13"/>
-      <c r="B33" s="14"/>
-      <c r="C33" s="14"/>
-      <c r="D33" s="14"/>
-      <c r="E33" s="14"/>
-      <c r="F33" s="14"/>
-      <c r="G33" s="14"/>
-      <c r="H33" s="14"/>
-      <c r="I33" s="15" t="str">
+    <row r="33" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A33" s="13">
+        <v>46273</v>
+      </c>
+      <c r="B33" s="14">
+        <v>300</v>
+      </c>
+      <c r="C33" s="14">
+        <v>40</v>
+      </c>
+      <c r="D33" s="14">
+        <v>60</v>
+      </c>
+      <c r="E33" s="14">
+        <v>20</v>
+      </c>
+      <c r="F33" s="14">
+        <v>350</v>
+      </c>
+      <c r="G33" s="14">
+        <v>7</v>
+      </c>
+      <c r="H33" s="14">
+        <v>180</v>
+      </c>
+      <c r="I33" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J33" s="15" t="str">
+        <v>950</v>
+      </c>
+      <c r="J33" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K33" s="16"/>
-      <c r="L33" s="16"/>
-      <c r="M33" s="16"/>
-      <c r="N33" s="17"/>
+        <v>490</v>
+      </c>
+      <c r="K33" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="L33" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="M33" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N33" s="17" t="s">
+        <v>70</v>
+      </c>
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A34" s="13"/>

--- a/CAP766(PYTHON).xlsx
+++ b/CAP766(PYTHON).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\asus\Desktop\776\CAP776-GROUP-I-\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{279AE183-E3CF-492B-909D-71457E01F329}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F469AEE-BB08-480C-936A-125C48989FCA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="83">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -272,6 +272,9 @@
   </si>
   <si>
     <t>completed my First CA test in networking.</t>
+  </si>
+  <si>
+    <t>….........</t>
   </si>
 </sst>
 </file>
@@ -2341,29 +2344,55 @@
       </c>
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A34" s="13"/>
-      <c r="B34" s="14"/>
-      <c r="C34" s="14"/>
-      <c r="D34" s="14"/>
-      <c r="E34" s="14"/>
-      <c r="F34" s="14"/>
-      <c r="G34" s="14"/>
-      <c r="H34" s="14"/>
-      <c r="I34" s="15" t="str">
+      <c r="A34" s="13">
+        <v>46274</v>
+      </c>
+      <c r="B34" s="14">
+        <v>300</v>
+      </c>
+      <c r="C34" s="14">
+        <v>40</v>
+      </c>
+      <c r="D34" s="14">
+        <v>120</v>
+      </c>
+      <c r="E34" s="14">
+        <v>20</v>
+      </c>
+      <c r="F34" s="14">
+        <v>200</v>
+      </c>
+      <c r="G34" s="14">
+        <v>4</v>
+      </c>
+      <c r="H34" s="14">
+        <v>240</v>
+      </c>
+      <c r="I34" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J34" s="15" t="str">
+        <v>920</v>
+      </c>
+      <c r="J34" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K34" s="16"/>
-      <c r="L34" s="16"/>
-      <c r="M34" s="16"/>
-      <c r="N34" s="17"/>
+        <v>520</v>
+      </c>
+      <c r="K34" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="L34" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="M34" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N34" s="17" t="s">
+        <v>82</v>
+      </c>
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A35" s="13"/>
+      <c r="A35" s="13">
+        <v>46275</v>
+      </c>
       <c r="B35" s="14"/>
       <c r="C35" s="14"/>
       <c r="D35" s="14"/>

--- a/CAP766(PYTHON).xlsx
+++ b/CAP766(PYTHON).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\asus\Desktop\776\CAP776-GROUP-I-\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F469AEE-BB08-480C-936A-125C48989FCA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EEA7B6B4-071A-4E81-B8B6-93AC4A42BD11}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="84">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -275,6 +275,9 @@
   </si>
   <si>
     <t>….........</t>
+  </si>
+  <si>
+    <t>prep for CA TEST.</t>
   </si>
 </sst>
 </file>
@@ -2393,25 +2396,47 @@
       <c r="A35" s="13">
         <v>46275</v>
       </c>
-      <c r="B35" s="14"/>
-      <c r="C35" s="14"/>
-      <c r="D35" s="14"/>
-      <c r="E35" s="14"/>
-      <c r="F35" s="14"/>
-      <c r="G35" s="14"/>
-      <c r="H35" s="14"/>
-      <c r="I35" s="15" t="str">
+      <c r="B35" s="14">
+        <v>300</v>
+      </c>
+      <c r="C35" s="14">
+        <v>40</v>
+      </c>
+      <c r="D35" s="14">
+        <v>180</v>
+      </c>
+      <c r="E35" s="14">
+        <v>30</v>
+      </c>
+      <c r="F35" s="14">
+        <v>350</v>
+      </c>
+      <c r="G35" s="14">
+        <v>7</v>
+      </c>
+      <c r="H35" s="14">
+        <v>120</v>
+      </c>
+      <c r="I35" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J35" s="15" t="str">
+        <v>1020</v>
+      </c>
+      <c r="J35" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K35" s="16"/>
-      <c r="L35" s="16"/>
-      <c r="M35" s="16"/>
-      <c r="N35" s="17"/>
+        <v>420</v>
+      </c>
+      <c r="K35" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L35" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="M35" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N35" s="17" t="s">
+        <v>83</v>
+      </c>
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A36" s="13"/>

--- a/CAP766(PYTHON).xlsx
+++ b/CAP766(PYTHON).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\asus\Desktop\776\CAP776-GROUP-I-\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EEA7B6B4-071A-4E81-B8B6-93AC4A42BD11}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87FC94FD-047A-4520-80F4-2CCB932129B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="185" uniqueCount="86">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -278,6 +278,12 @@
   </si>
   <si>
     <t>prep for CA TEST.</t>
+  </si>
+  <si>
+    <t>….....</t>
+  </si>
+  <si>
+    <t>enjoy the whole day in watching series.</t>
   </si>
 </sst>
 </file>
@@ -2439,87 +2445,165 @@
       </c>
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A36" s="13"/>
-      <c r="B36" s="14"/>
-      <c r="C36" s="14"/>
-      <c r="D36" s="14"/>
-      <c r="E36" s="14"/>
-      <c r="F36" s="14"/>
-      <c r="G36" s="14"/>
-      <c r="H36" s="14"/>
-      <c r="I36" s="15" t="str">
+      <c r="A36" s="13">
+        <v>46276</v>
+      </c>
+      <c r="B36" s="14">
+        <v>300</v>
+      </c>
+      <c r="C36" s="14">
+        <v>40</v>
+      </c>
+      <c r="D36" s="14">
+        <v>180</v>
+      </c>
+      <c r="E36" s="14">
+        <v>20</v>
+      </c>
+      <c r="F36" s="14">
+        <v>250</v>
+      </c>
+      <c r="G36" s="14">
+        <v>5</v>
+      </c>
+      <c r="H36" s="14">
+        <v>120</v>
+      </c>
+      <c r="I36" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J36" s="15" t="str">
+        <v>910</v>
+      </c>
+      <c r="J36" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K36" s="16"/>
-      <c r="L36" s="16"/>
-      <c r="M36" s="16"/>
-      <c r="N36" s="17"/>
+        <v>530</v>
+      </c>
+      <c r="K36" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="L36" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="M36" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N36" s="17" t="s">
+        <v>84</v>
+      </c>
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A37" s="13"/>
-      <c r="B37" s="14"/>
-      <c r="C37" s="14"/>
-      <c r="D37" s="14"/>
-      <c r="E37" s="14"/>
-      <c r="F37" s="14"/>
-      <c r="G37" s="14"/>
-      <c r="H37" s="14"/>
-      <c r="I37" s="15" t="str">
+      <c r="A37" s="13">
+        <v>46277</v>
+      </c>
+      <c r="B37" s="14">
+        <v>240</v>
+      </c>
+      <c r="C37" s="14">
+        <v>10</v>
+      </c>
+      <c r="D37" s="14">
+        <v>180</v>
+      </c>
+      <c r="E37" s="14">
+        <v>40</v>
+      </c>
+      <c r="F37" s="14">
+        <v>0</v>
+      </c>
+      <c r="G37" s="14">
+        <v>0</v>
+      </c>
+      <c r="H37" s="14">
+        <v>200</v>
+      </c>
+      <c r="I37" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J37" s="15" t="str">
+        <v>670</v>
+      </c>
+      <c r="J37" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K37" s="16"/>
-      <c r="L37" s="16"/>
-      <c r="M37" s="16"/>
-      <c r="N37" s="17"/>
-    </row>
-    <row r="38" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A38" s="13"/>
-      <c r="B38" s="14"/>
-      <c r="C38" s="14"/>
-      <c r="D38" s="14"/>
-      <c r="E38" s="14"/>
-      <c r="F38" s="14"/>
-      <c r="G38" s="14"/>
-      <c r="H38" s="14"/>
-      <c r="I38" s="15" t="str">
+        <v>770</v>
+      </c>
+      <c r="K37" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="L37" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="M37" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N37" s="17" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="38" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A38" s="13">
+        <v>46278</v>
+      </c>
+      <c r="B38" s="14">
+        <v>360</v>
+      </c>
+      <c r="C38" s="14">
+        <v>40</v>
+      </c>
+      <c r="D38" s="14">
+        <v>180</v>
+      </c>
+      <c r="E38" s="14">
+        <v>20</v>
+      </c>
+      <c r="F38" s="14">
+        <v>0</v>
+      </c>
+      <c r="G38" s="14">
+        <v>0</v>
+      </c>
+      <c r="H38" s="14">
+        <v>300</v>
+      </c>
+      <c r="I38" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J38" s="15" t="str">
+        <v>900</v>
+      </c>
+      <c r="J38" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K38" s="16"/>
-      <c r="L38" s="16"/>
-      <c r="M38" s="16"/>
-      <c r="N38" s="17"/>
+        <v>540</v>
+      </c>
+      <c r="K38" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="L38" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="M38" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N38" s="17" t="s">
+        <v>85</v>
+      </c>
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A39" s="13"/>
-      <c r="B39" s="14"/>
-      <c r="C39" s="14"/>
+      <c r="A39" s="13">
+        <v>46279</v>
+      </c>
+      <c r="B39" s="14">
+        <v>360</v>
+      </c>
+      <c r="C39" s="14">
+        <v>40</v>
+      </c>
       <c r="D39" s="14"/>
       <c r="E39" s="14"/>
       <c r="F39" s="14"/>
       <c r="G39" s="14"/>
       <c r="H39" s="14"/>
-      <c r="I39" s="15" t="str">
+      <c r="I39" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J39" s="15" t="str">
+        <v>400</v>
+      </c>
+      <c r="J39" s="15">
         <f t="shared" si="1"/>
-        <v/>
+        <v>1040</v>
       </c>
       <c r="K39" s="16"/>
       <c r="L39" s="16"/>
@@ -2527,7 +2611,9 @@
       <c r="N39" s="17"/>
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A40" s="13"/>
+      <c r="A40" s="13">
+        <v>46280</v>
+      </c>
       <c r="B40" s="14"/>
       <c r="C40" s="14"/>
       <c r="D40" s="14"/>

--- a/CAP766(PYTHON).xlsx
+++ b/CAP766(PYTHON).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\asus\Desktop\776\CAP776-GROUP-I-\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87FC94FD-047A-4520-80F4-2CCB932129B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B0CFBD3-3FFB-4C26-AD30-427B10A04EE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="185" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="88">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -284,6 +284,12 @@
   </si>
   <si>
     <t>enjoy the whole day in watching series.</t>
+  </si>
+  <si>
+    <t>OUT OF STATION.</t>
+  </si>
+  <si>
+    <t>completed my First CA test in python .</t>
   </si>
 </sst>
 </file>
@@ -2592,50 +2598,92 @@
       <c r="C39" s="14">
         <v>40</v>
       </c>
-      <c r="D39" s="14"/>
-      <c r="E39" s="14"/>
-      <c r="F39" s="14"/>
-      <c r="G39" s="14"/>
-      <c r="H39" s="14"/>
+      <c r="D39" s="14">
+        <v>60</v>
+      </c>
+      <c r="E39" s="14">
+        <v>0</v>
+      </c>
+      <c r="F39" s="14">
+        <v>0</v>
+      </c>
+      <c r="G39" s="14">
+        <v>0</v>
+      </c>
+      <c r="H39" s="14">
+        <v>600</v>
+      </c>
       <c r="I39" s="15">
         <f t="shared" si="0"/>
-        <v>400</v>
+        <v>1060</v>
       </c>
       <c r="J39" s="15">
         <f t="shared" si="1"/>
-        <v>1040</v>
-      </c>
-      <c r="K39" s="16"/>
-      <c r="L39" s="16"/>
-      <c r="M39" s="16"/>
-      <c r="N39" s="17"/>
-    </row>
-    <row r="40" spans="1:14" x14ac:dyDescent="0.3">
+        <v>380</v>
+      </c>
+      <c r="K39" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="L39" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="M39" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N39" s="17" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="40" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A40" s="13">
         <v>46280</v>
       </c>
-      <c r="B40" s="14"/>
-      <c r="C40" s="14"/>
-      <c r="D40" s="14"/>
-      <c r="E40" s="14"/>
-      <c r="F40" s="14"/>
-      <c r="G40" s="14"/>
-      <c r="H40" s="14"/>
-      <c r="I40" s="15" t="str">
+      <c r="B40" s="14">
+        <v>360</v>
+      </c>
+      <c r="C40" s="14">
+        <v>40</v>
+      </c>
+      <c r="D40" s="14">
+        <v>180</v>
+      </c>
+      <c r="E40" s="14">
+        <v>20</v>
+      </c>
+      <c r="F40" s="14">
+        <v>350</v>
+      </c>
+      <c r="G40" s="14">
+        <v>7</v>
+      </c>
+      <c r="H40" s="14">
+        <v>60</v>
+      </c>
+      <c r="I40" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J40" s="15" t="str">
+        <v>1010</v>
+      </c>
+      <c r="J40" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K40" s="16"/>
-      <c r="L40" s="16"/>
-      <c r="M40" s="16"/>
-      <c r="N40" s="17"/>
+        <v>430</v>
+      </c>
+      <c r="K40" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="L40" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="M40" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="N40" s="17" t="s">
+        <v>87</v>
+      </c>
     </row>
     <row r="41" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A41" s="13"/>
+      <c r="A41" s="13">
+        <v>46281</v>
+      </c>
       <c r="B41" s="14"/>
       <c r="C41" s="14"/>
       <c r="D41" s="14"/>
@@ -2657,7 +2705,9 @@
       <c r="N41" s="17"/>
     </row>
     <row r="42" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A42" s="13"/>
+      <c r="A42" s="13">
+        <v>46282</v>
+      </c>
       <c r="B42" s="14"/>
       <c r="C42" s="14"/>
       <c r="D42" s="14"/>
@@ -2679,7 +2729,9 @@
       <c r="N42" s="17"/>
     </row>
     <row r="43" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A43" s="13"/>
+      <c r="A43" s="13">
+        <v>46283</v>
+      </c>
       <c r="B43" s="14"/>
       <c r="C43" s="14"/>
       <c r="D43" s="14"/>
@@ -2701,7 +2753,9 @@
       <c r="N43" s="17"/>
     </row>
     <row r="44" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A44" s="13"/>
+      <c r="A44" s="13">
+        <v>46284</v>
+      </c>
       <c r="B44" s="14"/>
       <c r="C44" s="14"/>
       <c r="D44" s="14"/>

--- a/CAP766(PYTHON).xlsx
+++ b/CAP766(PYTHON).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\asus\Desktop\776\CAP776-GROUP-I-\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B0CFBD3-3FFB-4C26-AD30-427B10A04EE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A334CCD-255B-4D66-95E3-C386051B5EB1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="213" uniqueCount="92">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -196,9 +196,6 @@
     <t>MCA/D1P2635</t>
   </si>
   <si>
-    <t>August</t>
-  </si>
-  <si>
     <t>Low</t>
   </si>
   <si>
@@ -290,6 +287,21 @@
   </si>
   <si>
     <t>completed my First CA test in python .</t>
+  </si>
+  <si>
+    <t>…......!!!!!</t>
+  </si>
+  <si>
+    <t>August,September</t>
+  </si>
+  <si>
+    <t>started understanding depth concepts in c++</t>
+  </si>
+  <si>
+    <t>Math CA done.</t>
+  </si>
+  <si>
+    <t>understanding concepts of oops.</t>
   </si>
 </sst>
 </file>
@@ -1004,7 +1016,7 @@
         <v>33</v>
       </c>
       <c r="F3" s="20" t="s">
-        <v>56</v>
+        <v>88</v>
       </c>
       <c r="G3" s="20"/>
     </row>
@@ -1150,16 +1162,16 @@
         <v>400</v>
       </c>
       <c r="K7" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="L7" s="16" t="s">
         <v>57</v>
       </c>
-      <c r="L7" s="16" t="s">
-        <v>58</v>
-      </c>
       <c r="M7" s="16" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="N7" s="17" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="8" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
@@ -1196,16 +1208,16 @@
         <v>260</v>
       </c>
       <c r="K8" s="16" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="L8" s="16" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="M8" s="16" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="N8" s="17" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.3">
@@ -1245,13 +1257,13 @@
         <v>49</v>
       </c>
       <c r="L9" s="16" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="M9" s="16" t="s">
         <v>51</v>
       </c>
       <c r="N9" s="17" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.3">
@@ -1291,13 +1303,13 @@
         <v>49</v>
       </c>
       <c r="L10" s="16" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="M10" s="16" t="s">
         <v>51</v>
       </c>
       <c r="N10" s="17" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.3">
@@ -1334,16 +1346,16 @@
         <v>540</v>
       </c>
       <c r="K11" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="L11" s="16" t="s">
         <v>59</v>
       </c>
-      <c r="L11" s="16" t="s">
+      <c r="M11" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="N11" s="17" t="s">
         <v>60</v>
-      </c>
-      <c r="M11" s="16" t="s">
-        <v>57</v>
-      </c>
-      <c r="N11" s="17" t="s">
-        <v>61</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.3">
@@ -1380,16 +1392,16 @@
         <v>455</v>
       </c>
       <c r="K12" s="16" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="L12" s="16" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="M12" s="16" t="s">
         <v>51</v>
       </c>
       <c r="N12" s="17" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.3">
@@ -1429,13 +1441,13 @@
         <v>49</v>
       </c>
       <c r="L13" s="16" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="M13" s="16" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="N13" s="17" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.3">
@@ -1472,16 +1484,16 @@
         <v>475</v>
       </c>
       <c r="K14" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="L14" s="16" t="s">
         <v>57</v>
-      </c>
-      <c r="L14" s="16" t="s">
-        <v>58</v>
       </c>
       <c r="M14" s="16" t="s">
         <v>51</v>
       </c>
       <c r="N14" s="17" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.3">
@@ -1518,16 +1530,16 @@
         <v>530</v>
       </c>
       <c r="K15" s="16" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="L15" s="16" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="M15" s="16" t="s">
         <v>51</v>
       </c>
       <c r="N15" s="17" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.3">
@@ -1564,16 +1576,16 @@
         <v>830</v>
       </c>
       <c r="K16" s="16" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="L16" s="16" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="M16" s="16" t="s">
         <v>51</v>
       </c>
       <c r="N16" s="17" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.3">
@@ -1613,13 +1625,13 @@
         <v>49</v>
       </c>
       <c r="L17" s="16" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="M17" s="16" t="s">
         <v>51</v>
       </c>
       <c r="N17" s="17" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.3">
@@ -1665,7 +1677,7 @@
         <v>51</v>
       </c>
       <c r="N18" s="17" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.3">
@@ -1705,13 +1717,13 @@
         <v>49</v>
       </c>
       <c r="L19" s="16" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="M19" s="16" t="s">
         <v>51</v>
       </c>
       <c r="N19" s="17" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="20" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
@@ -1748,16 +1760,16 @@
         <v>580</v>
       </c>
       <c r="K20" s="16" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="L20" s="16" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="M20" s="16" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="N20" s="17" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="21" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
@@ -1797,13 +1809,13 @@
         <v>49</v>
       </c>
       <c r="L21" s="16" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="M21" s="16" t="s">
         <v>51</v>
       </c>
       <c r="N21" s="17" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.3">
@@ -1840,16 +1852,16 @@
         <v>620</v>
       </c>
       <c r="K22" s="16" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="L22" s="16" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="M22" s="16" t="s">
         <v>51</v>
       </c>
       <c r="N22" s="17" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.3">
@@ -1886,7 +1898,7 @@
         <v>760</v>
       </c>
       <c r="K23" s="16" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="L23" s="16" t="s">
         <v>50</v>
@@ -1895,7 +1907,7 @@
         <v>51</v>
       </c>
       <c r="N23" s="17" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.3">
@@ -1932,16 +1944,16 @@
         <v>705</v>
       </c>
       <c r="K24" s="16" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="L24" s="16" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="M24" s="16" t="s">
         <v>51</v>
       </c>
       <c r="N24" s="17" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.3">
@@ -1978,16 +1990,16 @@
         <v>655</v>
       </c>
       <c r="K25" s="16" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="L25" s="16" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="M25" s="16" t="s">
         <v>51</v>
       </c>
       <c r="N25" s="17" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="26" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
@@ -2024,16 +2036,16 @@
         <v>350</v>
       </c>
       <c r="K26" s="16" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="L26" s="16" t="s">
         <v>50</v>
       </c>
       <c r="M26" s="16" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="N26" s="17" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="27" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
@@ -2073,13 +2085,13 @@
         <v>49</v>
       </c>
       <c r="L27" s="16" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="M27" s="16" t="s">
         <v>51</v>
       </c>
       <c r="N27" s="17" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.3">
@@ -2116,7 +2128,7 @@
         <v>360</v>
       </c>
       <c r="K28" s="16" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="L28" s="16" t="s">
         <v>50</v>
@@ -2125,7 +2137,7 @@
         <v>51</v>
       </c>
       <c r="N28" s="17" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="29" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
@@ -2162,16 +2174,16 @@
         <v>520</v>
       </c>
       <c r="K29" s="16" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="L29" s="16" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="M29" s="16" t="s">
         <v>51</v>
       </c>
       <c r="N29" s="17" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.3">
@@ -2208,16 +2220,16 @@
         <v>660</v>
       </c>
       <c r="K30" s="16" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="L30" s="16" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="M30" s="16" t="s">
         <v>51</v>
       </c>
       <c r="N30" s="17" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.3">
@@ -2257,13 +2269,13 @@
         <v>49</v>
       </c>
       <c r="L31" s="16" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="M31" s="16" t="s">
         <v>51</v>
       </c>
       <c r="N31" s="17" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="32" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
@@ -2300,16 +2312,16 @@
         <v>590</v>
       </c>
       <c r="K32" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="L32" s="16" t="s">
         <v>57</v>
-      </c>
-      <c r="L32" s="16" t="s">
-        <v>58</v>
       </c>
       <c r="M32" s="16" t="s">
         <v>51</v>
       </c>
       <c r="N32" s="17" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="33" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
@@ -2346,16 +2358,16 @@
         <v>490</v>
       </c>
       <c r="K33" s="16" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="L33" s="16" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="M33" s="16" t="s">
         <v>51</v>
       </c>
       <c r="N33" s="17" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.3">
@@ -2392,16 +2404,16 @@
         <v>520</v>
       </c>
       <c r="K34" s="16" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="L34" s="16" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="M34" s="16" t="s">
         <v>51</v>
       </c>
       <c r="N34" s="17" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.3">
@@ -2441,13 +2453,13 @@
         <v>49</v>
       </c>
       <c r="L35" s="16" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="M35" s="16" t="s">
         <v>51</v>
       </c>
       <c r="N35" s="17" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.3">
@@ -2484,16 +2496,16 @@
         <v>530</v>
       </c>
       <c r="K36" s="16" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="L36" s="16" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="M36" s="16" t="s">
         <v>51</v>
       </c>
       <c r="N36" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.3">
@@ -2530,16 +2542,16 @@
         <v>770</v>
       </c>
       <c r="K37" s="16" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="L37" s="16" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="M37" s="16" t="s">
         <v>51</v>
       </c>
       <c r="N37" s="17" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="38" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
@@ -2576,16 +2588,16 @@
         <v>540</v>
       </c>
       <c r="K38" s="16" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="L38" s="16" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="M38" s="16" t="s">
         <v>51</v>
       </c>
       <c r="N38" s="17" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.3">
@@ -2622,16 +2634,16 @@
         <v>380</v>
       </c>
       <c r="K39" s="16" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="L39" s="16" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="M39" s="16" t="s">
         <v>51</v>
       </c>
       <c r="N39" s="17" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="40" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
@@ -2668,135 +2680,247 @@
         <v>430</v>
       </c>
       <c r="K40" s="16" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="L40" s="16" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="M40" s="16" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="N40" s="17" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="41" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A41" s="13">
         <v>46281</v>
       </c>
-      <c r="B41" s="14"/>
-      <c r="C41" s="14"/>
-      <c r="D41" s="14"/>
-      <c r="E41" s="14"/>
-      <c r="F41" s="14"/>
-      <c r="G41" s="14"/>
-      <c r="H41" s="14"/>
-      <c r="I41" s="15" t="str">
+      <c r="B41" s="14">
+        <v>360</v>
+      </c>
+      <c r="C41" s="14">
+        <v>40</v>
+      </c>
+      <c r="D41" s="14">
+        <v>180</v>
+      </c>
+      <c r="E41" s="14">
+        <v>20</v>
+      </c>
+      <c r="F41" s="14">
+        <v>240</v>
+      </c>
+      <c r="G41" s="14">
+        <v>4</v>
+      </c>
+      <c r="H41" s="14">
+        <v>240</v>
+      </c>
+      <c r="I41" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J41" s="15" t="str">
+        <v>1080</v>
+      </c>
+      <c r="J41" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K41" s="16"/>
-      <c r="L41" s="16"/>
-      <c r="M41" s="16"/>
-      <c r="N41" s="17"/>
+        <v>360</v>
+      </c>
+      <c r="K41" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="L41" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="M41" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N41" s="17" t="s">
+        <v>64</v>
+      </c>
     </row>
     <row r="42" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A42" s="13">
         <v>46282</v>
       </c>
-      <c r="B42" s="14"/>
-      <c r="C42" s="14"/>
-      <c r="D42" s="14"/>
-      <c r="E42" s="14"/>
-      <c r="F42" s="14"/>
-      <c r="G42" s="14"/>
-      <c r="H42" s="14"/>
-      <c r="I42" s="15" t="str">
+      <c r="B42" s="14">
+        <v>360</v>
+      </c>
+      <c r="C42" s="14">
+        <v>40</v>
+      </c>
+      <c r="D42" s="14">
+        <v>180</v>
+      </c>
+      <c r="E42" s="14">
+        <v>15</v>
+      </c>
+      <c r="F42" s="14">
+        <v>350</v>
+      </c>
+      <c r="G42" s="14">
+        <v>7</v>
+      </c>
+      <c r="H42" s="14">
+        <v>240</v>
+      </c>
+      <c r="I42" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J42" s="15" t="str">
+        <v>1185</v>
+      </c>
+      <c r="J42" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K42" s="16"/>
-      <c r="L42" s="16"/>
-      <c r="M42" s="16"/>
-      <c r="N42" s="17"/>
-    </row>
-    <row r="43" spans="1:14" x14ac:dyDescent="0.3">
+        <v>255</v>
+      </c>
+      <c r="K42" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L42" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="M42" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N42" s="17" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="43" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A43" s="13">
         <v>46283</v>
       </c>
-      <c r="B43" s="14"/>
-      <c r="C43" s="14"/>
-      <c r="D43" s="14"/>
-      <c r="E43" s="14"/>
-      <c r="F43" s="14"/>
-      <c r="G43" s="14"/>
-      <c r="H43" s="14"/>
-      <c r="I43" s="15" t="str">
+      <c r="B43" s="14">
+        <v>360</v>
+      </c>
+      <c r="C43" s="14">
+        <v>40</v>
+      </c>
+      <c r="D43" s="14">
+        <v>210</v>
+      </c>
+      <c r="E43" s="14">
+        <v>120</v>
+      </c>
+      <c r="F43" s="14">
+        <v>350</v>
+      </c>
+      <c r="G43" s="14">
+        <v>7</v>
+      </c>
+      <c r="H43" s="14">
+        <v>210</v>
+      </c>
+      <c r="I43" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J43" s="15" t="str">
+        <v>1290</v>
+      </c>
+      <c r="J43" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K43" s="16"/>
-      <c r="L43" s="16"/>
-      <c r="M43" s="16"/>
-      <c r="N43" s="17"/>
+        <v>150</v>
+      </c>
+      <c r="K43" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L43" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="M43" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N43" s="17" t="s">
+        <v>89</v>
+      </c>
     </row>
     <row r="44" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A44" s="13">
         <v>46284</v>
       </c>
-      <c r="B44" s="14"/>
-      <c r="C44" s="14"/>
-      <c r="D44" s="14"/>
-      <c r="E44" s="14"/>
-      <c r="F44" s="14"/>
-      <c r="G44" s="14"/>
-      <c r="H44" s="14"/>
-      <c r="I44" s="15" t="str">
+      <c r="B44" s="14">
+        <v>300</v>
+      </c>
+      <c r="C44" s="14">
+        <v>40</v>
+      </c>
+      <c r="D44" s="14">
+        <v>280</v>
+      </c>
+      <c r="E44" s="14">
+        <v>120</v>
+      </c>
+      <c r="F44" s="14">
+        <v>100</v>
+      </c>
+      <c r="G44" s="14">
+        <v>2</v>
+      </c>
+      <c r="H44" s="14">
+        <v>120</v>
+      </c>
+      <c r="I44" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J44" s="15" t="str">
+        <v>960</v>
+      </c>
+      <c r="J44" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K44" s="16"/>
-      <c r="L44" s="16"/>
-      <c r="M44" s="16"/>
-      <c r="N44" s="17"/>
+        <v>480</v>
+      </c>
+      <c r="K44" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="L44" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="M44" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N44" s="17" t="s">
+        <v>90</v>
+      </c>
     </row>
     <row r="45" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A45" s="13"/>
-      <c r="B45" s="14"/>
-      <c r="C45" s="14"/>
-      <c r="D45" s="14"/>
-      <c r="E45" s="14"/>
-      <c r="F45" s="14"/>
-      <c r="G45" s="14"/>
-      <c r="H45" s="14"/>
-      <c r="I45" s="15" t="str">
+      <c r="A45" s="13">
+        <v>46285</v>
+      </c>
+      <c r="B45" s="14">
+        <v>300</v>
+      </c>
+      <c r="C45" s="14">
+        <v>0</v>
+      </c>
+      <c r="D45" s="14">
+        <v>280</v>
+      </c>
+      <c r="E45" s="14">
+        <v>180</v>
+      </c>
+      <c r="F45" s="14">
+        <v>0</v>
+      </c>
+      <c r="G45" s="14">
+        <v>0</v>
+      </c>
+      <c r="H45" s="14">
+        <v>200</v>
+      </c>
+      <c r="I45" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J45" s="15" t="str">
+        <v>960</v>
+      </c>
+      <c r="J45" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K45" s="16"/>
-      <c r="L45" s="16"/>
-      <c r="M45" s="16"/>
-      <c r="N45" s="17"/>
+        <v>480</v>
+      </c>
+      <c r="K45" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="L45" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="M45" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N45" s="17" t="s">
+        <v>91</v>
+      </c>
     </row>
     <row r="46" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A46" s="13"/>

--- a/CAP766(PYTHON).xlsx
+++ b/CAP766(PYTHON).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\asus\Desktop\776\CAP776-GROUP-I-\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A334CCD-255B-4D66-95E3-C386051B5EB1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8251776-D75F-40B8-B72D-56CB9213B71B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="213" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="217" uniqueCount="93">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -302,6 +302,9 @@
   </si>
   <si>
     <t>understanding concepts of oops.</t>
+  </si>
+  <si>
+    <t>clearing concepts of python.</t>
   </si>
 </sst>
 </file>
@@ -2923,26 +2926,50 @@
       </c>
     </row>
     <row r="46" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A46" s="13"/>
-      <c r="B46" s="14"/>
-      <c r="C46" s="14"/>
-      <c r="D46" s="14"/>
-      <c r="E46" s="14"/>
-      <c r="F46" s="14"/>
-      <c r="G46" s="14"/>
-      <c r="H46" s="14"/>
-      <c r="I46" s="15" t="str">
+      <c r="A46" s="13">
+        <v>46286</v>
+      </c>
+      <c r="B46" s="14">
+        <v>360</v>
+      </c>
+      <c r="C46" s="14">
+        <v>40</v>
+      </c>
+      <c r="D46" s="14">
+        <v>210</v>
+      </c>
+      <c r="E46" s="14">
+        <v>120</v>
+      </c>
+      <c r="F46" s="14">
+        <v>100</v>
+      </c>
+      <c r="G46" s="14">
+        <v>2</v>
+      </c>
+      <c r="H46" s="14">
+        <v>120</v>
+      </c>
+      <c r="I46" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J46" s="15" t="str">
+        <v>950</v>
+      </c>
+      <c r="J46" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K46" s="16"/>
-      <c r="L46" s="16"/>
-      <c r="M46" s="16"/>
-      <c r="N46" s="17"/>
+        <v>490</v>
+      </c>
+      <c r="K46" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="L46" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="M46" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N46" s="17" t="s">
+        <v>92</v>
+      </c>
     </row>
     <row r="47" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A47" s="13"/>
